--- a/Requisitos CIERRE/proceso edicion macros 1.xlsx
+++ b/Requisitos CIERRE/proceso edicion macros 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Requisitos CIERRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Requisitos CIERRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1BBA45-5A3E-445D-97C7-973594B7DF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD780CF-8F85-4ACF-AA7F-02F6D28AE8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -233,13 +233,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,1017 +584,1021 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640CE446-AF02-4226-AEA3-E9E69120384E}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="B2:G60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="42.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B1" s="1">
         <v>2666</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="D1" s="1">
         <v>72</v>
       </c>
-      <c r="G2" s="1">
+      <c r="E1" s="2">
         <v>42863</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="B2" s="1">
         <v>216</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="D2" s="1">
         <v>64</v>
       </c>
-      <c r="G3" s="1">
+      <c r="E2" s="2">
         <v>42866</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="B3" s="1">
         <v>119</v>
       </c>
-      <c r="E4" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="D3" s="1">
         <v>63</v>
       </c>
-      <c r="G4" s="1">
+      <c r="E3" s="2">
         <v>42867</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="B4" s="1">
         <v>177</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="D4" s="1">
         <v>75</v>
       </c>
-      <c r="G5" s="1">
+      <c r="E4" s="2">
         <v>42867</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="B5" s="1">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="D5" s="1">
         <v>69</v>
       </c>
-      <c r="G6" s="1">
+      <c r="E5" s="2">
         <v>42881</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="B6" s="1">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F7">
+      <c r="D6" s="1">
         <v>63</v>
       </c>
-      <c r="G7" s="1">
+      <c r="E6" s="2">
         <v>43059</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="B7" s="1">
         <v>2667</v>
       </c>
-      <c r="E8" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F8">
+      <c r="D7" s="1">
         <v>61</v>
       </c>
-      <c r="G8" s="1">
+      <c r="E7" s="2">
         <v>43116</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>8</v>
       </c>
-      <c r="D9">
+      <c r="B8" s="1">
         <v>169</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F9">
+      <c r="D8" s="1">
         <v>61</v>
       </c>
-      <c r="G9" s="1">
+      <c r="E8" s="2">
         <v>43118</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>9</v>
       </c>
-      <c r="D10">
+      <c r="B9" s="1">
         <v>72</v>
       </c>
-      <c r="E10" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="D9" s="1">
         <v>82</v>
       </c>
-      <c r="G10" s="1">
+      <c r="E9" s="2">
         <v>43229</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="B10" s="1">
         <v>170</v>
       </c>
-      <c r="E11" t="s">
+      <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F11">
+      <c r="D10" s="1">
         <v>61</v>
       </c>
-      <c r="G11" s="1">
+      <c r="E10" s="2">
         <v>43294</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="B11" s="1">
         <v>178</v>
       </c>
-      <c r="E12" t="s">
+      <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F12">
+      <c r="D11" s="1">
         <v>68</v>
       </c>
-      <c r="G12" s="1">
+      <c r="E11" s="2">
         <v>43423</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>12</v>
       </c>
-      <c r="D13">
+      <c r="B12" s="1">
         <v>85</v>
       </c>
-      <c r="E13" t="s">
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F13">
+      <c r="D12" s="1">
         <v>65</v>
       </c>
-      <c r="G13" s="1">
+      <c r="E12" s="2">
         <v>43425</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>13</v>
       </c>
-      <c r="D14">
+      <c r="B13" s="1">
         <v>146</v>
       </c>
-      <c r="E14" t="s">
+      <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F14">
+      <c r="D13" s="1">
         <v>63</v>
       </c>
-      <c r="G14" s="1">
+      <c r="E13" s="2">
         <v>43483</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>14</v>
       </c>
-      <c r="D15">
+      <c r="B14" s="1">
         <v>290</v>
       </c>
-      <c r="E15" t="s">
+      <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F15">
+      <c r="D14" s="1">
         <v>61</v>
       </c>
-      <c r="G15" s="1">
+      <c r="E14" s="2">
         <v>43787</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>15</v>
       </c>
-      <c r="D16">
+      <c r="B15" s="1">
         <v>949</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16">
+      <c r="D15" s="1">
         <v>61</v>
       </c>
-      <c r="G16" s="1">
+      <c r="E15" s="2">
         <v>43963</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>16</v>
       </c>
-      <c r="D17">
+      <c r="B16" s="1">
         <v>292</v>
       </c>
-      <c r="E17" t="s">
+      <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F17">
+      <c r="D16" s="1">
         <v>77</v>
       </c>
-      <c r="G17" s="1">
+      <c r="E16" s="2">
         <v>43964</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>17</v>
       </c>
-      <c r="D18">
+      <c r="B17" s="1">
         <v>147</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F18">
+      <c r="D17" s="1">
         <v>79</v>
       </c>
-      <c r="G18" s="1">
+      <c r="E17" s="2">
         <v>44011</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>18</v>
       </c>
-      <c r="D19">
+      <c r="B18" s="1">
         <v>291</v>
       </c>
-      <c r="E19" t="s">
+      <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19">
+      <c r="D18" s="1">
         <v>61</v>
       </c>
-      <c r="G19" s="1">
+      <c r="E18" s="2">
         <v>44011</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>19</v>
       </c>
-      <c r="D20">
+      <c r="B19" s="1">
         <v>673</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F20">
+      <c r="D19" s="1">
         <v>68</v>
       </c>
-      <c r="G20" s="1">
+      <c r="E19" s="2">
         <v>44139</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>20</v>
       </c>
-      <c r="D21">
+      <c r="B20" s="1">
         <v>674</v>
       </c>
-      <c r="E21" t="s">
+      <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
+      <c r="D20" s="1">
         <v>64</v>
       </c>
-      <c r="G21" s="1">
+      <c r="E20" s="2">
         <v>44145</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>21</v>
       </c>
-      <c r="D22">
+      <c r="B21" s="1">
         <v>670</v>
       </c>
-      <c r="E22" t="s">
+      <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F22">
+      <c r="D21" s="1">
         <v>80</v>
       </c>
-      <c r="G22" s="1">
+      <c r="E21" s="2">
         <v>44211</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
         <v>22</v>
       </c>
-      <c r="D23">
+      <c r="B22" s="1">
         <v>694</v>
       </c>
-      <c r="E23" t="s">
+      <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F23">
+      <c r="D22" s="1">
         <v>70</v>
       </c>
-      <c r="G23" s="1">
+      <c r="E22" s="2">
         <v>44504</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>23</v>
       </c>
-      <c r="D24">
+      <c r="B23" s="1">
         <v>94</v>
       </c>
-      <c r="E24" t="s">
+      <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F24">
+      <c r="D23" s="1">
         <v>61</v>
       </c>
-      <c r="G24" s="1">
+      <c r="E23" s="2">
         <v>44693</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>24</v>
       </c>
-      <c r="D25">
+      <c r="B24" s="1">
         <v>87</v>
       </c>
-      <c r="E25" t="s">
+      <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F25">
+      <c r="D24" s="1">
         <v>63</v>
       </c>
-      <c r="G25" s="1">
+      <c r="E24" s="2">
         <v>45054</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>25</v>
       </c>
-      <c r="D26">
+      <c r="B25" s="1">
         <v>2394</v>
       </c>
-      <c r="E26" t="s">
+      <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F26">
+      <c r="D25" s="1">
         <v>71</v>
       </c>
-      <c r="G26" s="1">
+      <c r="E25" s="2">
         <v>45054</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>26</v>
       </c>
-      <c r="D27">
+      <c r="B26" s="1">
         <v>217</v>
       </c>
-      <c r="E27" t="s">
+      <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F27">
+      <c r="D26" s="1">
         <v>68</v>
       </c>
-      <c r="G27" s="1">
+      <c r="E26" s="2">
         <v>45055</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>27</v>
       </c>
-      <c r="D28">
+      <c r="B27" s="1">
         <v>680</v>
       </c>
-      <c r="E28" t="s">
+      <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F28">
+      <c r="D27" s="1">
         <v>72</v>
       </c>
-      <c r="G28" s="1">
+      <c r="E27" s="2">
         <v>45055</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>28</v>
       </c>
-      <c r="D29">
+      <c r="B28" s="1">
         <v>746</v>
       </c>
-      <c r="E29" t="s">
+      <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F29">
+      <c r="D28" s="1">
         <v>69</v>
       </c>
-      <c r="G29" s="1">
+      <c r="E28" s="2">
         <v>45058</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
         <v>29</v>
       </c>
-      <c r="D30">
+      <c r="B29" s="1">
         <v>109</v>
       </c>
-      <c r="E30" t="s">
+      <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F30">
+      <c r="D29" s="1">
         <v>68</v>
       </c>
-      <c r="G30" s="1">
+      <c r="E29" s="2">
         <v>45068</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>30</v>
       </c>
-      <c r="D31">
+      <c r="B30" s="1">
         <v>672</v>
       </c>
-      <c r="E31" t="s">
+      <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F31">
+      <c r="D30" s="1">
         <v>81</v>
       </c>
-      <c r="G31" s="1">
+      <c r="E30" s="2">
         <v>45106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
         <v>31</v>
       </c>
-      <c r="D32">
+      <c r="B31" s="1">
         <v>690</v>
       </c>
-      <c r="E32" t="s">
+      <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F32">
+      <c r="D31" s="1">
         <v>65</v>
       </c>
-      <c r="G32" s="1">
+      <c r="E31" s="2">
         <v>45236</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
         <v>32</v>
       </c>
-      <c r="D33">
+      <c r="B32" s="1">
         <v>121</v>
       </c>
-      <c r="E33" t="s">
+      <c r="C32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F33">
+      <c r="D32" s="1">
         <v>66</v>
       </c>
-      <c r="G33" s="1">
+      <c r="E32" s="2">
         <v>45236</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>33</v>
       </c>
-      <c r="D34">
+      <c r="B33" s="1">
         <v>671</v>
       </c>
-      <c r="E34" t="s">
+      <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F34">
+      <c r="D33" s="1">
         <v>63</v>
       </c>
-      <c r="G34" s="1">
+      <c r="E33" s="2">
         <v>45238</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>34</v>
       </c>
-      <c r="D35">
+      <c r="B34" s="1">
         <v>679</v>
       </c>
-      <c r="E35" t="s">
+      <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F35">
+      <c r="D34" s="1">
         <v>71</v>
       </c>
-      <c r="G35" s="1">
+      <c r="E34" s="2">
         <v>45239</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>35</v>
       </c>
-      <c r="D36">
+      <c r="B35" s="1">
         <v>748</v>
       </c>
-      <c r="E36" t="s">
+      <c r="C35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F36">
+      <c r="D35" s="1">
         <v>76</v>
       </c>
-      <c r="G36" s="1">
+      <c r="E35" s="2">
         <v>45239</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
         <v>36</v>
       </c>
-      <c r="D37">
+      <c r="B36" s="1">
         <v>764</v>
       </c>
-      <c r="E37" t="s">
+      <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F37">
+      <c r="D36" s="1">
         <v>76</v>
       </c>
-      <c r="G37" s="1">
+      <c r="E36" s="2">
         <v>45240</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>37</v>
       </c>
-      <c r="D38">
+      <c r="B37" s="1">
         <v>677</v>
       </c>
-      <c r="E38" t="s">
+      <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F38">
+      <c r="D37" s="1">
         <v>63</v>
       </c>
-      <c r="G38" s="1">
+      <c r="E37" s="2">
         <v>45251</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>38</v>
       </c>
-      <c r="D39">
+      <c r="B38" s="1">
         <v>2585</v>
       </c>
-      <c r="E39" t="s">
+      <c r="C38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F39">
+      <c r="D38" s="1">
         <v>89</v>
       </c>
-      <c r="G39" s="1">
+      <c r="E38" s="2">
         <v>45253</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>39</v>
       </c>
-      <c r="D40">
+      <c r="B39" s="1">
         <v>686</v>
       </c>
-      <c r="E40" t="s">
+      <c r="C39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F40">
+      <c r="D39" s="1">
         <v>61</v>
       </c>
-      <c r="G40" s="1">
+      <c r="E39" s="2">
         <v>45289</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
         <v>40</v>
       </c>
-      <c r="D41">
+      <c r="B40" s="1">
         <v>945</v>
       </c>
-      <c r="E41" t="s">
+      <c r="C40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F41">
+      <c r="D40" s="1">
         <v>88</v>
       </c>
-      <c r="G41" s="1">
+      <c r="E40" s="2">
         <v>45418</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
         <v>41</v>
       </c>
-      <c r="D42">
+      <c r="B41" s="1">
         <v>935</v>
       </c>
-      <c r="E42" t="s">
+      <c r="C41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F42">
+      <c r="D41" s="1">
         <v>83</v>
       </c>
-      <c r="G42" s="1">
+      <c r="E41" s="2">
         <v>45419</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
         <v>42</v>
       </c>
-      <c r="D43">
+      <c r="B42" s="1">
         <v>749</v>
       </c>
-      <c r="E43" t="s">
+      <c r="C42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F43">
+      <c r="D42" s="1">
         <v>87</v>
       </c>
-      <c r="G43" s="1">
+      <c r="E42" s="2">
         <v>45422</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
         <v>43</v>
       </c>
-      <c r="D44">
+      <c r="B43" s="1">
         <v>747</v>
       </c>
-      <c r="E44" t="s">
+      <c r="C43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F44">
+      <c r="D43" s="1">
         <v>82</v>
       </c>
-      <c r="G44" s="1">
+      <c r="E43" s="2">
         <v>45436</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
         <v>44</v>
       </c>
-      <c r="D45">
+      <c r="B44" s="1">
         <v>943</v>
       </c>
-      <c r="E45" t="s">
+      <c r="C44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F45">
+      <c r="D44" s="1">
         <v>68</v>
       </c>
-      <c r="G45" s="1">
+      <c r="E44" s="2">
         <v>45436</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
         <v>45</v>
       </c>
-      <c r="D46">
+      <c r="B45" s="1">
         <v>745</v>
       </c>
-      <c r="E46" t="s">
+      <c r="C45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F46">
+      <c r="D45" s="1">
         <v>79</v>
       </c>
-      <c r="G46" s="1">
+      <c r="E45" s="2">
         <v>45471</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
         <v>46</v>
       </c>
-      <c r="D47">
+      <c r="B46" s="1">
         <v>940</v>
       </c>
-      <c r="E47" t="s">
+      <c r="C46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F47">
+      <c r="D46" s="1">
         <v>81</v>
       </c>
-      <c r="G47" s="1">
+      <c r="E46" s="2">
         <v>45471</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>47</v>
       </c>
-      <c r="D48">
+      <c r="B47" s="1">
         <v>932</v>
       </c>
-      <c r="E48" t="s">
+      <c r="C47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F48">
+      <c r="D47" s="1">
         <v>61</v>
       </c>
-      <c r="G48" s="1">
+      <c r="E47" s="2">
         <v>45600</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
         <v>48</v>
       </c>
-      <c r="D49">
+      <c r="B48" s="1">
         <v>799</v>
       </c>
-      <c r="E49" t="s">
+      <c r="C48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F49">
+      <c r="D48" s="1">
         <v>61</v>
       </c>
-      <c r="G49" s="1">
+      <c r="E48" s="2">
         <v>45602</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
         <v>49</v>
       </c>
-      <c r="D50">
+      <c r="B49" s="1">
         <v>2671</v>
       </c>
-      <c r="E50" t="s">
+      <c r="C49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F50">
+      <c r="D49" s="1">
         <v>70</v>
       </c>
-      <c r="G50" s="1">
+      <c r="E49" s="2">
         <v>45602</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
         <v>50</v>
       </c>
-      <c r="D51">
+      <c r="B50" s="1">
         <v>798</v>
       </c>
-      <c r="E51" t="s">
+      <c r="C50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F51">
+      <c r="D50" s="1">
         <v>63</v>
       </c>
-      <c r="G51" s="1">
+      <c r="E50" s="2">
         <v>45615</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
         <v>51</v>
       </c>
-      <c r="D52">
+      <c r="B51" s="1">
         <v>791</v>
       </c>
-      <c r="E52" t="s">
+      <c r="C51" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F52">
+      <c r="D51" s="1">
         <v>65</v>
       </c>
-      <c r="G52" s="1">
+      <c r="E51" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
         <v>52</v>
       </c>
-      <c r="D53">
+      <c r="B52" s="1">
         <v>936</v>
       </c>
-      <c r="E53" t="s">
+      <c r="C52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F53">
+      <c r="D52" s="1">
         <v>84</v>
       </c>
-      <c r="G53" s="1">
+      <c r="E52" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
         <v>53</v>
       </c>
-      <c r="D54">
+      <c r="B53" s="1">
         <v>1071</v>
       </c>
-      <c r="E54" t="s">
+      <c r="C53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F54">
+      <c r="D53" s="1">
         <v>63</v>
       </c>
-      <c r="G54" s="1">
+      <c r="E53" s="2">
         <v>45782</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
         <v>54</v>
       </c>
-      <c r="D55">
+      <c r="B54" s="1">
         <v>1057</v>
       </c>
-      <c r="E55" t="s">
+      <c r="C54" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F55">
+      <c r="D54" s="1">
         <v>76</v>
       </c>
-      <c r="G55" s="1">
+      <c r="E54" s="2">
         <v>45784</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
         <v>55</v>
       </c>
-      <c r="D56">
+      <c r="B55" s="1">
         <v>912</v>
       </c>
-      <c r="E56" t="s">
+      <c r="C55" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F56">
+      <c r="D55" s="1">
         <v>79</v>
       </c>
-      <c r="G56" s="1">
+      <c r="E55" s="2">
         <v>45785</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
         <v>56</v>
       </c>
-      <c r="D57">
+      <c r="B56" s="1">
         <v>911</v>
       </c>
-      <c r="E57" t="s">
+      <c r="C56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F57">
+      <c r="D56" s="1">
         <v>62</v>
       </c>
-      <c r="G57" s="1">
+      <c r="E56" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B58">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
         <v>57</v>
       </c>
-      <c r="D58">
+      <c r="B57" s="1">
         <v>2860</v>
       </c>
-      <c r="E58" t="s">
+      <c r="C57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F58">
+      <c r="D57" s="1">
         <v>74</v>
       </c>
-      <c r="G58" s="1">
+      <c r="E57" s="2">
         <v>45835</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
         <v>58</v>
       </c>
-      <c r="D59">
+      <c r="B58" s="1">
         <v>2586</v>
       </c>
-      <c r="E59" t="s">
+      <c r="C58" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F59">
+      <c r="D58" s="1">
         <v>69</v>
       </c>
-      <c r="G59" s="1">
+      <c r="E58" s="2">
         <v>45967</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
         <v>59</v>
       </c>
-      <c r="D60">
+      <c r="B59" s="1">
         <v>906</v>
       </c>
-      <c r="E60" t="s">
+      <c r="C59" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F60">
+      <c r="D59" s="1">
         <v>62</v>
       </c>
-      <c r="G60" s="1">
+      <c r="E59" s="2">
         <v>46022</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Requisitos CIERRE/proceso edicion macros 1.xlsx
+++ b/Requisitos CIERRE/proceso edicion macros 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Requisitos CIERRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Requisitos CIERRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD780CF-8F85-4ACF-AA7F-02F6D28AE8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB30ABEE-995D-4279-9F97-58638AA39F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -261,14 +261,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,34 +767,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640CE446-AF02-4226-AEA3-E9E69120384E}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:F59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
-    <col min="3" max="3" width="42.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="6">
         <v>2666</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="6">
         <v>72</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="7">
         <v>42863</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>2</v>
       </c>
       <c r="B2" s="1">
@@ -627,9 +810,10 @@
       <c r="E2" s="2">
         <v>42866</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>3</v>
       </c>
       <c r="B3" s="1">
@@ -644,9 +828,10 @@
       <c r="E3" s="2">
         <v>42867</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -661,9 +846,10 @@
       <c r="E4" s="2">
         <v>42867</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>5</v>
       </c>
       <c r="B5" s="1">
@@ -678,9 +864,10 @@
       <c r="E5" s="2">
         <v>42881</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>6</v>
       </c>
       <c r="B6" s="1">
@@ -695,9 +882,10 @@
       <c r="E6" s="2">
         <v>43059</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>7</v>
       </c>
       <c r="B7" s="1">
@@ -712,76 +900,81 @@
       <c r="E7" s="2">
         <v>43116</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="12">
         <v>169</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="12">
         <v>61</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="13">
         <v>43118</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="6">
         <v>72</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="6">
         <v>82</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <v>43229</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="12">
         <v>170</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="12">
         <v>61</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="13">
         <v>43294</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>178</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="3">
         <v>68</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="4">
         <v>43423</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -798,7 +991,7 @@
         <v>43425</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -815,7 +1008,7 @@
         <v>43483</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -832,7 +1025,7 @@
         <v>43787</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -849,7 +1042,7 @@
         <v>43963</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -866,7 +1059,7 @@
         <v>43964</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -883,7 +1076,7 @@
         <v>44011</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -900,7 +1093,7 @@
         <v>44011</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -917,7 +1110,7 @@
         <v>44139</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -934,7 +1127,7 @@
         <v>44145</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -951,7 +1144,7 @@
         <v>44211</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -968,7 +1161,7 @@
         <v>44504</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -985,7 +1178,7 @@
         <v>44693</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -1002,7 +1195,7 @@
         <v>45054</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -1019,7 +1212,7 @@
         <v>45054</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -1036,7 +1229,7 @@
         <v>45055</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -1053,7 +1246,7 @@
         <v>45055</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -1070,7 +1263,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -1087,7 +1280,7 @@
         <v>45068</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -1104,7 +1297,7 @@
         <v>45106</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -1121,7 +1314,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -1138,7 +1331,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -1155,7 +1348,7 @@
         <v>45238</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -1172,7 +1365,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -1189,7 +1382,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -1206,7 +1399,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -1223,7 +1416,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -1240,7 +1433,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -1257,7 +1450,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -1274,7 +1467,7 @@
         <v>45418</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -1291,7 +1484,7 @@
         <v>45419</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -1308,7 +1501,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -1325,7 +1518,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -1342,7 +1535,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -1359,7 +1552,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -1376,7 +1569,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -1393,7 +1586,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -1410,7 +1603,7 @@
         <v>45602</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -1427,7 +1620,7 @@
         <v>45602</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -1444,7 +1637,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -1461,7 +1654,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -1478,7 +1671,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -1495,7 +1688,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -1512,7 +1705,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -1529,7 +1722,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -1546,7 +1739,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -1563,7 +1756,7 @@
         <v>45835</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -1580,7 +1773,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>59</v>
       </c>

--- a/Requisitos CIERRE/proceso edicion macros 1.xlsx
+++ b/Requisitos CIERRE/proceso edicion macros 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Requisitos CIERRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB30ABEE-995D-4279-9F97-58638AA39F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22EEE09-871F-4593-BFC8-3AD5B56C1C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>ORIENTACION Y LIDERAZGO</t>
   </si>
@@ -202,13 +202,25 @@
   </si>
   <si>
     <t>ANALISIS MECANICO</t>
+  </si>
+  <si>
+    <t>290 - 146</t>
+  </si>
+  <si>
+    <t>OBLIGATORIO</t>
+  </si>
+  <si>
+    <t>291 - 292</t>
+  </si>
+  <si>
+    <t>292 - 147</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,16 +228,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -431,26 +455,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,1031 +834,1154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640CE446-AF02-4226-AEA3-E9E69120384E}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="17"/>
+      <c r="C1" s="4">
         <v>2666</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6">
+      <c r="E1" s="4">
         <v>72</v>
       </c>
-      <c r="E1" s="7">
+      <c r="F1" s="5">
         <v>42863</v>
       </c>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="18"/>
+      <c r="C2" s="8">
         <v>216</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="8">
         <v>64</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="9">
         <v>42866</v>
       </c>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="18"/>
+      <c r="C3" s="8">
         <v>119</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="8">
         <v>63</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="9">
         <v>42867</v>
       </c>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="18"/>
+      <c r="C4" s="8">
         <v>177</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="8">
         <v>75</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="9">
         <v>42867</v>
       </c>
-      <c r="F4" s="10"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="18"/>
+      <c r="C5" s="8">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="8">
         <v>69</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="9">
         <v>42881</v>
       </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="18"/>
+      <c r="C6" s="8">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="8">
         <v>63</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="9">
         <v>43059</v>
       </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="18"/>
+      <c r="C7" s="8">
         <v>2667</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="8">
         <v>61</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="9">
         <v>43116</v>
       </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>8</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="19"/>
+      <c r="C8" s="12">
         <v>169</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="12">
+      <c r="E8" s="12">
         <v>61</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="13">
         <v>43118</v>
       </c>
-      <c r="F8" s="14"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="17"/>
+      <c r="C9" s="4">
         <v>72</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="4">
         <v>82</v>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="5">
         <v>43229</v>
       </c>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>10</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="19"/>
+      <c r="C10" s="12">
         <v>170</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="12">
+      <c r="E10" s="12">
         <v>61</v>
       </c>
-      <c r="E10" s="13">
+      <c r="F10" s="13">
         <v>43294</v>
       </c>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15">
         <v>178</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E11" s="15">
         <v>68</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="16">
         <v>43423</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8">
         <v>85</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="8">
         <v>65</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="9">
         <v>43425</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8">
         <v>146</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="8">
         <v>63</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="9">
         <v>43483</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
         <v>14</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8">
         <v>290</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="8">
         <v>61</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="9">
         <v>43787</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
         <v>15</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8">
         <v>949</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="8">
         <v>61</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="9">
         <v>43963</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
         <v>16</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8">
         <v>292</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="8">
         <v>77</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="9">
         <v>43964</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="1">
         <v>147</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <v>79</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>44011</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G17" s="1">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
       <c r="B18" s="1">
+        <v>290</v>
+      </c>
+      <c r="C18" s="1">
         <v>291</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>61</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>44011</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="1">
         <v>673</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E20" s="1">
         <v>68</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F20" s="2">
         <v>44139</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="G20" s="1">
+        <v>6</v>
+      </c>
+      <c r="H20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="1">
         <v>674</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E21" s="1">
         <v>64</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F21" s="2">
         <v>44145</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="G21" s="1">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="1">
         <v>670</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E22" s="1">
         <v>80</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F22" s="2">
         <v>44211</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="G22" s="1">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1">
         <v>694</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E24" s="1">
         <v>70</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F24" s="2">
         <v>44504</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1">
         <v>94</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E25" s="1">
         <v>61</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F25" s="2">
         <v>44693</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1">
         <v>87</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E26" s="1">
         <v>63</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F26" s="2">
         <v>45054</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1">
         <v>2394</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E27" s="1">
         <v>71</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F27" s="2">
         <v>45054</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1">
         <v>217</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E28" s="1">
         <v>68</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F28" s="2">
         <v>45055</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1">
         <v>680</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E29" s="1">
         <v>72</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F29" s="2">
         <v>45055</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1">
         <v>746</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E30" s="1">
         <v>69</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F30" s="2">
         <v>45058</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1">
         <v>109</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E31" s="1">
         <v>68</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F31" s="2">
         <v>45068</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1">
         <v>672</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E32" s="1">
         <v>81</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F32" s="2">
         <v>45106</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1">
         <v>690</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E33" s="1">
         <v>65</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F33" s="2">
         <v>45236</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1">
         <v>121</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E34" s="1">
         <v>66</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F34" s="2">
         <v>45236</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1">
         <v>671</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E35" s="1">
         <v>63</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F35" s="2">
         <v>45238</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1">
         <v>679</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E36" s="1">
         <v>71</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F36" s="2">
         <v>45239</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1">
         <v>748</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E37" s="1">
         <v>76</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F37" s="2">
         <v>45239</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1">
         <v>764</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E38" s="1">
         <v>76</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F38" s="2">
         <v>45240</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
         <v>677</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E39" s="1">
         <v>63</v>
       </c>
-      <c r="E37" s="2">
+      <c r="F39" s="2">
         <v>45251</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1">
         <v>2585</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E40" s="1">
         <v>89</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F40" s="2">
         <v>45253</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1">
         <v>686</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E41" s="1">
         <v>61</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F41" s="2">
         <v>45289</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1">
         <v>945</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E42" s="1">
         <v>88</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F42" s="2">
         <v>45418</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1">
         <v>935</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="1">
+      <c r="E43" s="1">
         <v>83</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F43" s="2">
         <v>45419</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1">
         <v>749</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="1">
+      <c r="E44" s="1">
         <v>87</v>
       </c>
-      <c r="E42" s="2">
+      <c r="F44" s="2">
         <v>45422</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1">
         <v>747</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="1">
+      <c r="E45" s="1">
         <v>82</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F45" s="2">
         <v>45436</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1">
         <v>943</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="1">
+      <c r="E46" s="1">
         <v>68</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F46" s="2">
         <v>45436</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1">
         <v>745</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="1">
+      <c r="E47" s="1">
         <v>79</v>
       </c>
-      <c r="E45" s="2">
+      <c r="F47" s="2">
         <v>45471</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1">
         <v>940</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="1">
+      <c r="E48" s="1">
         <v>81</v>
       </c>
-      <c r="E46" s="2">
+      <c r="F48" s="2">
         <v>45471</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1">
         <v>932</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E49" s="1">
         <v>61</v>
       </c>
-      <c r="E47" s="2">
+      <c r="F49" s="2">
         <v>45600</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1">
         <v>799</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E50" s="1">
         <v>61</v>
       </c>
-      <c r="E48" s="2">
+      <c r="F50" s="2">
         <v>45602</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1">
         <v>2671</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E51" s="1">
         <v>70</v>
       </c>
-      <c r="E49" s="2">
+      <c r="F51" s="2">
         <v>45602</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1">
         <v>798</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E52" s="1">
         <v>63</v>
       </c>
-      <c r="E50" s="2">
+      <c r="F52" s="2">
         <v>45615</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1">
         <v>791</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E53" s="1">
         <v>65</v>
       </c>
-      <c r="E51" s="2">
+      <c r="F53" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1">
         <v>936</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D52" s="1">
+      <c r="E54" s="1">
         <v>84</v>
       </c>
-      <c r="E52" s="2">
+      <c r="F54" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1">
         <v>1071</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E55" s="1">
         <v>63</v>
       </c>
-      <c r="E53" s="2">
+      <c r="F55" s="2">
         <v>45782</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1">
         <v>1057</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E56" s="1">
         <v>76</v>
       </c>
-      <c r="E54" s="2">
+      <c r="F56" s="2">
         <v>45784</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1">
         <v>912</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="1">
+      <c r="E57" s="1">
         <v>79</v>
       </c>
-      <c r="E55" s="2">
+      <c r="F57" s="2">
         <v>45785</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1">
         <v>911</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D56" s="1">
+      <c r="E58" s="1">
         <v>62</v>
       </c>
-      <c r="E56" s="2">
+      <c r="F58" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1">
         <v>2860</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D57" s="1">
+      <c r="E59" s="1">
         <v>74</v>
       </c>
-      <c r="E57" s="2">
+      <c r="F59" s="2">
         <v>45835</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1">
         <v>2586</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D58" s="1">
+      <c r="E60" s="1">
         <v>69</v>
       </c>
-      <c r="E58" s="2">
+      <c r="F60" s="2">
         <v>45967</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1">
         <v>906</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D59" s="1">
+      <c r="E61" s="1">
         <v>62</v>
       </c>
-      <c r="E59" s="2">
+      <c r="F61" s="2">
         <v>46022</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Requisitos CIERRE/proceso edicion macros 1.xlsx
+++ b/Requisitos CIERRE/proceso edicion macros 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Requisitos CIERRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22EEE09-871F-4593-BFC8-3AD5B56C1C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC0798-BE8F-4614-8D7F-6C65168E8664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
   <si>
     <t>ORIENTACION Y LIDERAZGO</t>
   </si>
@@ -214,6 +214,63 @@
   </si>
   <si>
     <t>292 - 147</t>
+  </si>
+  <si>
+    <t>90Cr</t>
+  </si>
+  <si>
+    <t>OPTATIVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBLIGATORIO </t>
+  </si>
+  <si>
+    <t>292 - 949</t>
+  </si>
+  <si>
+    <t>169 - 72 -216</t>
+  </si>
+  <si>
+    <t>292 - 109</t>
+  </si>
+  <si>
+    <t>2394 - 120Cr</t>
+  </si>
+  <si>
+    <t>165Cr</t>
+  </si>
+  <si>
+    <t>677 - 679</t>
+  </si>
+  <si>
+    <t>150Cr</t>
+  </si>
+  <si>
+    <t>747 - 748</t>
+  </si>
+  <si>
+    <t>745 - 935 - 679</t>
+  </si>
+  <si>
+    <t>748 - 935 -745</t>
+  </si>
+  <si>
+    <t>200Cr</t>
+  </si>
+  <si>
+    <t>190Cr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190Cr </t>
+  </si>
+  <si>
+    <t>109 - 745</t>
+  </si>
+  <si>
+    <t>2585 - 200Cr</t>
+  </si>
+  <si>
+    <t>932 -936</t>
   </si>
 </sst>
 </file>
@@ -353,21 +410,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -494,11 +536,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -506,19 +557,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -834,23 +901,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640CE446-AF02-4226-AEA3-E9E69120384E}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="4" max="4" width="42.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="1"/>
     <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="4">
         <v>2666</v>
       </c>
@@ -863,146 +931,162 @@
       <c r="F1" s="5">
         <v>42863</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="G1">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="8">
+      <c r="B2" s="15"/>
+      <c r="C2" s="7">
         <v>216</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>64</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>42866</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>3</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="8">
+      <c r="B3" s="15"/>
+      <c r="C3" s="7">
         <v>119</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>63</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>42867</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>4</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="8">
+      <c r="B4" s="15"/>
+      <c r="C4" s="7">
         <v>177</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>75</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>42867</v>
       </c>
-      <c r="G4" s="10"/>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>5</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="8">
+      <c r="B5" s="15"/>
+      <c r="C5" s="7">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>69</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>42881</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>6</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="8">
+      <c r="B6" s="15"/>
+      <c r="C6" s="7">
         <v>29</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>63</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>43059</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="23">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>7</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="8">
+      <c r="B7" s="15"/>
+      <c r="C7" s="7">
         <v>2667</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>61</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>43116</v>
       </c>
-      <c r="G7" s="10"/>
+      <c r="G7" s="23">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>8</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="12">
+      <c r="B8" s="16"/>
+      <c r="C8" s="10">
         <v>169</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>61</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <v>43118</v>
       </c>
-      <c r="G8" s="14"/>
+      <c r="G8" s="24">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>9</v>
       </c>
-      <c r="B9" s="17"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="4">
         <v>72</v>
       </c>
@@ -1015,972 +1099,1492 @@
       <c r="F9" s="5">
         <v>43229</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="23">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>10</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="12">
+      <c r="B10" s="16"/>
+      <c r="C10" s="10">
         <v>170</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>61</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="11">
         <v>43294</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="23">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="12">
         <v>11</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12">
         <v>178</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="12">
         <v>68</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="13">
         <v>43423</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="23">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>12</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7">
         <v>85</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>65</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>43425</v>
       </c>
-      <c r="G12" s="8"/>
+      <c r="G12" s="23">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>13</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7">
         <v>146</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>63</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>43483</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="25">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>14</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7">
         <v>290</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>61</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>43787</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="7">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>15</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7">
         <v>949</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>61</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>43963</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>16</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7">
         <v>292</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>77</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>43964</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="G16" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C18" s="7">
         <v>147</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18" s="7">
         <v>79</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F18" s="8">
         <v>44011</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="7">
         <v>6</v>
       </c>
-      <c r="H17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="H18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B19" s="21">
         <v>290</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C19" s="7">
         <v>291</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E19" s="7">
         <v>61</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F19" s="8">
         <v>44011</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G19" s="7">
         <v>5</v>
       </c>
-      <c r="H18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="H19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C21" s="7">
         <v>673</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E21" s="7">
         <v>68</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F21" s="8">
         <v>44139</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G21" s="7">
         <v>6</v>
       </c>
-      <c r="H20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="H21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C22" s="7">
         <v>674</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22" s="7">
         <v>64</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F22" s="8">
         <v>44145</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G22" s="7">
         <v>5</v>
       </c>
-      <c r="H21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="H22" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C23" s="7">
         <v>670</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E23" s="7">
         <v>80</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F23" s="8">
         <v>44211</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G23" s="7">
         <v>5</v>
       </c>
-      <c r="H22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="H23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="2"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1">
+      <c r="B25" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="7">
         <v>694</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E25" s="7">
         <v>70</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F25" s="8">
         <v>44504</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="G25" s="7">
+        <v>3</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
         <v>23</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1">
+      <c r="B27" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="7">
         <v>94</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E27" s="7">
         <v>61</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F27" s="8">
         <v>44693</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="G27" s="7">
+        <v>3</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
         <v>24</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1">
+      <c r="B29" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="7">
         <v>87</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D29" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E29" s="7">
         <v>63</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F29" s="8">
         <v>45054</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="G29" s="7">
+        <v>3</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
         <v>25</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1">
+      <c r="B30" s="21">
+        <v>170</v>
+      </c>
+      <c r="C30" s="7">
         <v>2394</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D30" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E30" s="7">
         <v>71</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F30" s="8">
         <v>45054</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1">
+      <c r="B31" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="7">
         <v>217</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D31" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E31" s="7">
         <v>68</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F31" s="8">
         <v>45055</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="G31" s="7">
+        <v>4</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" s="19"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
         <v>27</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1">
+      <c r="B32" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="7">
         <v>680</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D32" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E32" s="7">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F32" s="8">
         <v>45055</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="G32" s="7">
+        <v>3</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J32" s="19"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
         <v>28</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1">
+      <c r="B33" s="21">
+        <v>290</v>
+      </c>
+      <c r="C33" s="7">
         <v>746</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E33" s="7">
         <v>69</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F33" s="8">
         <v>45058</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="G33" s="7">
+        <v>6</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J33" s="19"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
         <v>29</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1">
+      <c r="B34" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="7">
         <v>109</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D34" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E34" s="7">
         <v>68</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F34" s="8">
         <v>45068</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="G34" s="7">
+        <v>5</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="19"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
         <v>30</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1">
+      <c r="B36" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="7">
         <v>672</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D36" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E36" s="7">
         <v>81</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F36" s="8">
         <v>45106</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="G36" s="7">
+        <v>5</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
         <v>31</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1">
+      <c r="B38" s="21">
+        <v>949</v>
+      </c>
+      <c r="C38" s="7">
         <v>690</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D38" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E38" s="7">
         <v>65</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F38" s="8">
         <v>45236</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="G38" s="7">
+        <v>5</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J38" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
         <v>32</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1">
+      <c r="B39" s="21">
+        <v>119</v>
+      </c>
+      <c r="C39" s="7">
         <v>121</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E39" s="7">
         <v>66</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F39" s="8">
         <v>45236</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="G39" s="7">
+        <v>3</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
         <v>33</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1">
+      <c r="B40" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="7">
         <v>671</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D40" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E40" s="7">
         <v>63</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F40" s="8">
         <v>45238</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="G40" s="7">
+        <v>6</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
         <v>34</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1">
+      <c r="B41" s="21">
+        <v>672</v>
+      </c>
+      <c r="C41" s="7">
         <v>679</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E41" s="7">
         <v>71</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F41" s="8">
         <v>45239</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="G41" s="7">
+        <v>6</v>
+      </c>
+      <c r="H41" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
         <v>35</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1">
+      <c r="B42" s="21">
+        <v>672</v>
+      </c>
+      <c r="C42" s="7">
         <v>748</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D42" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E42" s="7">
         <v>76</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F42" s="8">
         <v>45239</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="G42" s="7">
+        <v>5</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
         <v>36</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1">
+      <c r="B43" s="21">
+        <v>680</v>
+      </c>
+      <c r="C43" s="7">
         <v>764</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D43" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E43" s="7">
         <v>76</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F43" s="8">
         <v>45240</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="G43" s="7">
+        <v>3</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
         <v>37</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1">
+      <c r="B44" s="21">
+        <v>672</v>
+      </c>
+      <c r="C44" s="7">
         <v>677</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D44" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E44" s="7">
         <v>63</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F44" s="8">
         <v>45251</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="G44" s="7">
+        <v>5</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
         <v>38</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1">
+      <c r="B45" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="7">
         <v>2585</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D45" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E45" s="7">
         <v>89</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F45" s="8">
         <v>45253</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="G45" s="7">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
         <v>39</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1">
+      <c r="B47" s="21">
+        <v>671</v>
+      </c>
+      <c r="C47" s="7">
         <v>686</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D47" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E47" s="7">
         <v>61</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F47" s="8">
         <v>45289</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="G47" s="7">
+        <v>6</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
         <v>40</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1">
+      <c r="B49" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="7">
         <v>945</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D49" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E49" s="7">
         <v>88</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F49" s="8">
         <v>45418</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="G49" s="7">
+        <v>5</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J49" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
         <v>41</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1">
+      <c r="B50" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="7">
         <v>935</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D50" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E50" s="7">
         <v>83</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F50" s="8">
         <v>45419</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="G50" s="7">
+        <v>5</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J50" s="19"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
         <v>42</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1">
+      <c r="B51" s="21">
+        <v>686</v>
+      </c>
+      <c r="C51" s="7">
         <v>749</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E51" s="7">
         <v>87</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F51" s="8">
         <v>45422</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="G51" s="7">
+        <v>6</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J51" s="19"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
         <v>43</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1">
+      <c r="B52" s="21">
+        <v>746</v>
+      </c>
+      <c r="C52" s="7">
         <v>747</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D52" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E52" s="7">
         <v>82</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F52" s="8">
         <v>45436</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="G52" s="7">
+        <v>6</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J52" s="19"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
         <v>44</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1">
+      <c r="B53" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="7">
         <v>943</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D53" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E53" s="7">
         <v>68</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F53" s="8">
         <v>45436</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="G53" s="7">
+        <v>5</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J53" s="19"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
         <v>45</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1">
+      <c r="B55" s="21">
+        <v>677</v>
+      </c>
+      <c r="C55" s="7">
         <v>745</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D55" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E55" s="7">
         <v>79</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F55" s="8">
         <v>45471</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="G55" s="7">
+        <v>6</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J55" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
         <v>46</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1">
+      <c r="B56" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="7">
         <v>940</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D56" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E56" s="7">
         <v>81</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F56" s="8">
         <v>45471</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="G56" s="7">
+        <v>6</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J56" s="19"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1">
+      <c r="B58" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="1">
         <v>932</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E58" s="1">
         <v>61</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F58" s="2">
         <v>45600</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="G58" s="1">
+        <v>5</v>
+      </c>
+      <c r="H58" t="s">
+        <v>60</v>
+      </c>
+      <c r="J58" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1">
+      <c r="B59" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="1">
         <v>799</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E59" s="1">
         <v>61</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F59" s="2">
         <v>45602</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="G59" s="1">
+        <v>5</v>
+      </c>
+      <c r="H59" t="s">
+        <v>60</v>
+      </c>
+      <c r="J59" s="19"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1">
+      <c r="B60" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="1">
         <v>2671</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E60" s="1">
         <v>70</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F60" s="2">
         <v>45602</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="G60" s="1">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>60</v>
+      </c>
+      <c r="J60" s="19"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1">
+      <c r="B61" s="17">
+        <v>749</v>
+      </c>
+      <c r="C61" s="1">
         <v>798</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E61" s="1">
         <v>63</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F61" s="2">
         <v>45615</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="G61" s="1">
+        <v>5</v>
+      </c>
+      <c r="H61" t="s">
+        <v>60</v>
+      </c>
+      <c r="J61" s="19"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1">
+      <c r="B63" s="17">
+        <v>749</v>
+      </c>
+      <c r="C63" s="1">
         <v>791</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E63" s="1">
         <v>65</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F63" s="2">
         <v>45657</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" t="s">
+        <v>65</v>
+      </c>
+      <c r="J63" s="19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>52</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1">
+      <c r="B64" s="17">
+        <v>935</v>
+      </c>
+      <c r="C64" s="1">
         <v>936</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E64" s="1">
         <v>84</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F64" s="2">
         <v>45657</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="G64" s="1">
+        <v>5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>65</v>
+      </c>
+      <c r="J64" s="19"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>53</v>
       </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1">
+      <c r="B66" s="17">
+        <v>799</v>
+      </c>
+      <c r="C66" s="1">
         <v>1071</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E66" s="1">
         <v>63</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F66" s="2">
         <v>45782</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="G66" s="1">
+        <v>5</v>
+      </c>
+      <c r="H66" t="s">
+        <v>60</v>
+      </c>
+      <c r="J66" s="19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>54</v>
       </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1">
+      <c r="B67" s="17">
+        <v>932</v>
+      </c>
+      <c r="C67" s="1">
         <v>1057</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E67" s="1">
         <v>76</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F67" s="2">
         <v>45784</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="G67" s="1">
+        <v>5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>60</v>
+      </c>
+      <c r="J67" s="19"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>55</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1">
+      <c r="B68" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="1">
         <v>912</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E68" s="1">
         <v>79</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F68" s="2">
         <v>45785</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="G68" s="1">
+        <v>6</v>
+      </c>
+      <c r="H68" t="s">
+        <v>60</v>
+      </c>
+      <c r="J68" s="19"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1">
+      <c r="B69" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="1">
         <v>911</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E69" s="1">
         <v>62</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F69" s="2">
         <v>45796</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="G69" s="1">
+        <v>6</v>
+      </c>
+      <c r="H69" t="s">
+        <v>60</v>
+      </c>
+      <c r="J69" s="19"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>57</v>
       </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1">
+      <c r="B71" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="1">
         <v>2860</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E71" s="1">
         <v>74</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F71" s="2">
         <v>45835</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="G71" s="1">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>60</v>
+      </c>
+      <c r="J71" s="20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>58</v>
       </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1">
+      <c r="B73" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="1">
         <v>2586</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E73" s="1">
         <v>69</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F73" s="2">
         <v>45967</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>60</v>
+      </c>
+      <c r="J73" s="20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>59</v>
       </c>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1">
+      <c r="B75" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="1">
         <v>906</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E75" s="1">
         <v>62</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F75" s="2">
         <v>46022</v>
       </c>
+      <c r="G75" s="1">
+        <v>6</v>
+      </c>
+      <c r="H75" t="s">
+        <v>60</v>
+      </c>
+      <c r="J75" s="20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="18"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G78" s="1">
+        <f>SUM(G1:G75)</f>
+        <v>262</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="J58:J61"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="J66:J69"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="J29:J34"/>
+    <mergeCell ref="J38:J45"/>
+    <mergeCell ref="J49:J53"/>
+    <mergeCell ref="J55:J56"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Requisitos CIERRE/proceso edicion macros 1.xlsx
+++ b/Requisitos CIERRE/proceso edicion macros 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Requisitos CIERRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Requisitos CIERRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC0798-BE8F-4614-8D7F-6C65168E8664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0240DCF4-F203-4ACC-93C6-863DD2E6D7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{753D117D-00DE-45A9-A86E-748C69335B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
   <si>
     <t>ORIENTACION Y LIDERAZGO</t>
   </si>
@@ -222,9 +222,6 @@
     <t>OPTATIVO</t>
   </si>
   <si>
-    <t xml:space="preserve">OBLIGATORIO </t>
-  </si>
-  <si>
     <t>292 - 949</t>
   </si>
   <si>
@@ -271,6 +268,12 @@
   </si>
   <si>
     <t>932 -936</t>
+  </si>
+  <si>
+    <t>NINGUNO</t>
+  </si>
+  <si>
+    <t>170  - 72</t>
   </si>
 </sst>
 </file>
@@ -306,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -487,45 +490,6 @@
         <color indexed="64"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -553,31 +517,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -585,7 +531,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,1609 +865,1943 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640CE446-AF02-4226-AEA3-E9E69120384E}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:J78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="20"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3">
-        <v>1</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1">
         <v>2666</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>72</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1" s="12">
         <v>42863</v>
       </c>
       <c r="G1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="25">
+        <f>COUNTIF(H1,"OBLIGATORIO")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="7">
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2">
         <v>216</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>64</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="12">
         <v>42866</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="25">
+        <f t="shared" ref="J2:J65" si="0">COUNTIF(H2,"OBLIGATORIO")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="7">
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3">
         <v>119</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3">
         <v>63</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="12">
         <v>42867</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="7">
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4">
         <v>177</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <v>75</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="12">
         <v>42867</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="7">
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>69</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="12">
         <v>42881</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="H5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>6</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="7">
+      <c r="B6">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1">
         <v>29</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="1">
         <v>63</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="2">
         <v>43059</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>7</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="7">
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="1">
         <v>2667</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="1">
         <v>61</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="2">
         <v>43116</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="9">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="H7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
         <v>8</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="10">
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="15">
         <v>169</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="15">
         <v>61</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="16">
         <v>43118</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="H8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
         <v>9</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="4">
+      <c r="B9">
+        <v>169</v>
+      </c>
+      <c r="C9" s="18">
         <v>72</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="18">
         <v>82</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="19">
         <v>43229</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
         <v>10</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="10">
+      <c r="B10">
+        <v>169</v>
+      </c>
+      <c r="C10" s="15">
         <v>170</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="15">
         <v>61</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="16">
         <v>43294</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="9">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="20">
         <v>11</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12">
+      <c r="B11">
+        <v>177</v>
+      </c>
+      <c r="C11" s="20">
         <v>178</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="20">
         <v>68</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="21">
         <v>43423</v>
       </c>
-      <c r="G11" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>12</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7">
+      <c r="B12" s="22">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1">
         <v>85</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="1">
         <v>65</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="2">
         <v>43425</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7">
+      <c r="B13" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="1">
         <v>146</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="1">
         <v>63</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="2">
         <v>43483</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="11">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>14</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7">
+      <c r="B14">
+        <v>170</v>
+      </c>
+      <c r="C14" s="1">
         <v>290</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="1">
         <v>61</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="2">
         <v>43787</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="11">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="H14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>15</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7">
+      <c r="B15">
+        <v>290</v>
+      </c>
+      <c r="C15" s="1">
         <v>949</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="1">
         <v>61</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="2">
         <v>43963</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>16</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7">
+      <c r="B16">
+        <v>290</v>
+      </c>
+      <c r="C16" s="1">
         <v>292</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="1">
         <v>77</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="2">
         <v>43964</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="H16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="3"/>
+      <c r="J17" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="3">
         <v>147</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="3">
         <v>79</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="4">
         <v>44011</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="3">
         <v>6</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J18" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="H18" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="7">
         <v>290</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>291</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="3">
         <v>61</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="4">
         <v>44011</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="3">
         <v>5</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="17"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="J20" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>19</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>673</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="3">
         <v>68</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="4">
         <v>44139</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="3">
         <v>6</v>
       </c>
-      <c r="H21" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="H21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>20</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>674</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="3">
         <v>64</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="4">
         <v>44145</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="3">
         <v>5</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J22" s="19"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="H22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="24">
+        <v>1</v>
+      </c>
+      <c r="J22" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>21</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>670</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>80</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="4">
         <v>44211</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="3">
         <v>5</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="19"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="17"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
-      <c r="J24" s="19"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="J24" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>694</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>70</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="4">
         <v>44504</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="3">
         <v>3</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="24">
+        <v>1</v>
+      </c>
+      <c r="J25" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="17"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="J26" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
         <v>23</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>94</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="3">
         <v>61</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="4">
         <v>44693</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="3">
         <v>3</v>
       </c>
-      <c r="H27" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H27" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="17"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="J28" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
         <v>24</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="3">
+        <v>87</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="3">
+        <v>63</v>
+      </c>
+      <c r="F29" s="4">
+        <v>45054</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J29" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>25</v>
+      </c>
+      <c r="B30" s="7">
+        <v>170</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2394</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="3">
+        <v>71</v>
+      </c>
+      <c r="F30" s="4">
+        <v>45054</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="7">
-        <v>87</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="7">
+      <c r="C31" s="3">
+        <v>217</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>68</v>
+      </c>
+      <c r="F31" s="4">
+        <v>45055</v>
+      </c>
+      <c r="G31" s="3">
+        <v>4</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="24">
+        <v>1</v>
+      </c>
+      <c r="J31" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>27</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F29" s="8">
-        <v>45054</v>
-      </c>
-      <c r="G29" s="7">
+      <c r="C32" s="3">
+        <v>680</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>72</v>
+      </c>
+      <c r="F32" s="4">
+        <v>45055</v>
+      </c>
+      <c r="G32" s="3">
         <v>3</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="J29" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>25</v>
-      </c>
-      <c r="B30" s="21">
-        <v>170</v>
-      </c>
-      <c r="C30" s="7">
-        <v>2394</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="7">
-        <v>71</v>
-      </c>
-      <c r="F30" s="8">
-        <v>45054</v>
-      </c>
-      <c r="G30" s="7">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J30" s="19"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>26</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="7">
-        <v>217</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="7">
+      <c r="H32" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J32" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>28</v>
+      </c>
+      <c r="B33" s="7">
+        <v>290</v>
+      </c>
+      <c r="C33" s="3">
+        <v>746</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="3">
+        <v>69</v>
+      </c>
+      <c r="F33" s="4">
+        <v>45058</v>
+      </c>
+      <c r="G33" s="3">
+        <v>6</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J33" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>29</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="3">
+        <v>109</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="3">
         <v>68</v>
       </c>
-      <c r="F31" s="8">
-        <v>45055</v>
-      </c>
-      <c r="G31" s="7">
-        <v>4</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="19"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>27</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="7">
-        <v>680</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="7">
-        <v>72</v>
-      </c>
-      <c r="F32" s="8">
-        <v>45055</v>
-      </c>
-      <c r="G32" s="7">
-        <v>3</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J32" s="19"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>28</v>
-      </c>
-      <c r="B33" s="21">
-        <v>290</v>
-      </c>
-      <c r="C33" s="7">
-        <v>746</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="7">
-        <v>69</v>
-      </c>
-      <c r="F33" s="8">
-        <v>45058</v>
-      </c>
-      <c r="G33" s="7">
-        <v>6</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J33" s="19"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>29</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="7">
-        <v>109</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="7">
-        <v>68</v>
-      </c>
-      <c r="F34" s="8">
+      <c r="F34" s="4">
         <v>45068</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="3">
         <v>5</v>
       </c>
-      <c r="H34" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J34" s="19"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H34" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="17"/>
+      <c r="B35" s="5"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="J35" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
         <v>30</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="7">
+      <c r="B36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="3">
         <v>672</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="3">
         <v>81</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="4">
         <v>45106</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="3">
         <v>5</v>
       </c>
-      <c r="H36" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H36" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J36" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="17"/>
+      <c r="B37" s="5"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="J37" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
         <v>31</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="7">
         <v>949</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="3">
         <v>690</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="3">
         <v>65</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="4">
         <v>45236</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="3">
         <v>5</v>
       </c>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J38" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="I38" s="24">
+        <v>1</v>
+      </c>
+      <c r="J38" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
         <v>32</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="7">
         <v>119</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="3">
         <v>121</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="3">
         <v>66</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="4">
         <v>45236</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="3">
         <v>3</v>
       </c>
-      <c r="H39" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J39" s="19"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="H39" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J39" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
         <v>33</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="3">
+        <v>671</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="3">
+        <v>63</v>
+      </c>
+      <c r="F40" s="4">
+        <v>45238</v>
+      </c>
+      <c r="G40" s="3">
+        <v>6</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J40" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>34</v>
+      </c>
+      <c r="B41" s="7">
+        <v>672</v>
+      </c>
+      <c r="C41" s="3">
+        <v>679</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="3">
+        <v>71</v>
+      </c>
+      <c r="F41" s="4">
+        <v>45239</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J41" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>35</v>
+      </c>
+      <c r="B42" s="7">
+        <v>672</v>
+      </c>
+      <c r="C42" s="3">
+        <v>748</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="3">
+        <v>76</v>
+      </c>
+      <c r="F42" s="4">
+        <v>45239</v>
+      </c>
+      <c r="G42" s="3">
+        <v>5</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J42" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>36</v>
+      </c>
+      <c r="B43" s="7">
+        <v>680</v>
+      </c>
+      <c r="C43" s="3">
+        <v>764</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="3">
+        <v>76</v>
+      </c>
+      <c r="F43" s="4">
+        <v>45240</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I43" s="24">
+        <v>1</v>
+      </c>
+      <c r="J43" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>37</v>
+      </c>
+      <c r="B44" s="7">
+        <v>672</v>
+      </c>
+      <c r="C44" s="3">
+        <v>677</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="3">
+        <v>63</v>
+      </c>
+      <c r="F44" s="4">
+        <v>45251</v>
+      </c>
+      <c r="G44" s="3">
+        <v>5</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J44" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>38</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="7">
-        <v>671</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E40" s="7">
-        <v>63</v>
-      </c>
-      <c r="F40" s="8">
-        <v>45238</v>
-      </c>
-      <c r="G40" s="7">
-        <v>6</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>34</v>
-      </c>
-      <c r="B41" s="21">
-        <v>672</v>
-      </c>
-      <c r="C41" s="7">
-        <v>679</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="7">
-        <v>71</v>
-      </c>
-      <c r="F41" s="8">
-        <v>45239</v>
-      </c>
-      <c r="G41" s="7">
-        <v>6</v>
-      </c>
-      <c r="H41" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J41" s="19"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>35</v>
-      </c>
-      <c r="B42" s="21">
-        <v>672</v>
-      </c>
-      <c r="C42" s="7">
-        <v>748</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="7">
-        <v>76</v>
-      </c>
-      <c r="F42" s="8">
-        <v>45239</v>
-      </c>
-      <c r="G42" s="7">
-        <v>5</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J42" s="19"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>36</v>
-      </c>
-      <c r="B43" s="21">
-        <v>680</v>
-      </c>
-      <c r="C43" s="7">
-        <v>764</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="7">
-        <v>76</v>
-      </c>
-      <c r="F43" s="8">
-        <v>45240</v>
-      </c>
-      <c r="G43" s="7">
-        <v>3</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J43" s="19"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="C45" s="3">
+        <v>2585</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="21">
-        <v>672</v>
-      </c>
-      <c r="C44" s="7">
-        <v>677</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="7">
-        <v>63</v>
-      </c>
-      <c r="F44" s="8">
-        <v>45251</v>
-      </c>
-      <c r="G44" s="7">
-        <v>5</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J44" s="19"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>38</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="7">
-        <v>2585</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="7">
+      <c r="E45" s="3">
         <v>89</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="4">
         <v>45253</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J45" s="19"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H45" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J45" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="17"/>
+      <c r="B46" s="5"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="J46" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
         <v>39</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="7">
         <v>671</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="3">
         <v>686</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="3">
         <v>61</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="4">
         <v>45289</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="3">
         <v>6</v>
       </c>
-      <c r="H47" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="J47" s="20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H47" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J47" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="17"/>
+      <c r="B48" s="5"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="J48" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
         <v>40</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="3">
+        <v>945</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="3">
+        <v>88</v>
+      </c>
+      <c r="F49" s="4">
+        <v>45418</v>
+      </c>
+      <c r="G49" s="3">
+        <v>5</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J49" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>41</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="7">
-        <v>945</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="7">
-        <v>88</v>
-      </c>
-      <c r="F49" s="8">
-        <v>45418</v>
-      </c>
-      <c r="G49" s="7">
+      <c r="C50" s="3">
+        <v>935</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="3">
+        <v>83</v>
+      </c>
+      <c r="F50" s="4">
+        <v>45419</v>
+      </c>
+      <c r="G50" s="3">
         <v>5</v>
       </c>
-      <c r="H49" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J49" s="19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="H50" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J50" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <v>42</v>
+      </c>
+      <c r="B51" s="7">
+        <v>686</v>
+      </c>
+      <c r="C51" s="3">
+        <v>749</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="E51" s="3">
+        <v>87</v>
+      </c>
+      <c r="F51" s="4">
+        <v>45422</v>
+      </c>
+      <c r="G51" s="3">
+        <v>6</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J51" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>43</v>
+      </c>
+      <c r="B52" s="7">
+        <v>746</v>
+      </c>
+      <c r="C52" s="3">
+        <v>747</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="3">
+        <v>82</v>
+      </c>
+      <c r="F52" s="4">
+        <v>45436</v>
+      </c>
+      <c r="G52" s="3">
+        <v>6</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J52" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <v>44</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="7">
-        <v>935</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" s="7">
-        <v>83</v>
-      </c>
-      <c r="F50" s="8">
-        <v>45419</v>
-      </c>
-      <c r="G50" s="7">
+      <c r="C53" s="3">
+        <v>943</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="3">
+        <v>68</v>
+      </c>
+      <c r="F53" s="4">
+        <v>45436</v>
+      </c>
+      <c r="G53" s="3">
         <v>5</v>
       </c>
-      <c r="H50" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J50" s="19"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>42</v>
-      </c>
-      <c r="B51" s="21">
-        <v>686</v>
-      </c>
-      <c r="C51" s="7">
-        <v>749</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51" s="7">
-        <v>87</v>
-      </c>
-      <c r="F51" s="8">
-        <v>45422</v>
-      </c>
-      <c r="G51" s="7">
-        <v>6</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J51" s="19"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>43</v>
-      </c>
-      <c r="B52" s="21">
-        <v>746</v>
-      </c>
-      <c r="C52" s="7">
-        <v>747</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" s="7">
-        <v>82</v>
-      </c>
-      <c r="F52" s="8">
-        <v>45436</v>
-      </c>
-      <c r="G52" s="7">
-        <v>6</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J52" s="19"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
-        <v>44</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="7">
-        <v>943</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="7">
-        <v>68</v>
-      </c>
-      <c r="F53" s="8">
-        <v>45436</v>
-      </c>
-      <c r="G53" s="7">
-        <v>5</v>
-      </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J53" s="19"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I53" s="24">
+        <v>1</v>
+      </c>
+      <c r="J53" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="17"/>
+      <c r="B54" s="5"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="J54" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
         <v>45</v>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="7">
         <v>677</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="3">
         <v>745</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="3">
         <v>79</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="4">
         <v>45471</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="3">
         <v>6</v>
       </c>
-      <c r="H55" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J55" s="19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+      <c r="H55" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J55" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
         <v>46</v>
       </c>
-      <c r="B56" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="7">
+      <c r="B56" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="3">
         <v>940</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="3">
         <v>81</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="4">
         <v>45471</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="3">
         <v>6</v>
       </c>
-      <c r="H56" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J56" s="19"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H56" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J56" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
-      <c r="B57" s="17"/>
+      <c r="B57" s="5"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="J57" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
         <v>47</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="3">
+        <v>932</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="3">
+        <v>61</v>
+      </c>
+      <c r="F58" s="4">
+        <v>45600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J58" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>48</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="1">
-        <v>932</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="C59" s="3">
+        <v>799</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="3">
         <v>61</v>
       </c>
-      <c r="F58" s="2">
-        <v>45600</v>
-      </c>
-      <c r="G58" s="1">
+      <c r="F59" s="4">
+        <v>45602</v>
+      </c>
+      <c r="G59" s="3">
         <v>5</v>
       </c>
-      <c r="H58" t="s">
-        <v>60</v>
-      </c>
-      <c r="J58" s="19">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="H59" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J59" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>49</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2671</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="1">
-        <v>799</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="1">
-        <v>61</v>
-      </c>
-      <c r="F59" s="2">
+      <c r="E60" s="3">
+        <v>70</v>
+      </c>
+      <c r="F60" s="4">
         <v>45602</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G60" s="3">
+        <v>4</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J60" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
+        <v>50</v>
+      </c>
+      <c r="B61" s="7">
+        <v>749</v>
+      </c>
+      <c r="C61" s="3">
+        <v>798</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="3">
+        <v>63</v>
+      </c>
+      <c r="F61" s="4">
+        <v>45615</v>
+      </c>
+      <c r="G61" s="3">
         <v>5</v>
       </c>
-      <c r="H59" t="s">
-        <v>60</v>
-      </c>
-      <c r="J59" s="19"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>49</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" s="1">
-        <v>2671</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="1">
-        <v>70</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45602</v>
-      </c>
-      <c r="G60" s="1">
-        <v>4</v>
-      </c>
-      <c r="H60" t="s">
-        <v>60</v>
-      </c>
-      <c r="J60" s="19"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>50</v>
-      </c>
-      <c r="B61" s="17">
-        <v>749</v>
-      </c>
-      <c r="C61" s="1">
-        <v>798</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" s="1">
-        <v>63</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45615</v>
-      </c>
-      <c r="G61" s="1">
-        <v>5</v>
-      </c>
-      <c r="H61" t="s">
-        <v>60</v>
-      </c>
-      <c r="J61" s="19"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H61" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J61" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
-      <c r="B62" s="17"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="J62" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
         <v>51</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="7">
         <v>749</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="3">
         <v>791</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="3">
         <v>65</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>45657</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="3">
         <v>5</v>
       </c>
-      <c r="H63" t="s">
-        <v>65</v>
-      </c>
-      <c r="J63" s="19">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="H63" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J63" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
         <v>52</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="7">
         <v>935</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="3">
         <v>936</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="3">
         <v>84</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>45657</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="3">
         <v>5</v>
       </c>
-      <c r="H64" t="s">
-        <v>65</v>
-      </c>
-      <c r="J64" s="19"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H64" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J64" s="25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
-      <c r="B65" s="17"/>
+      <c r="B65" s="5"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="J65" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
         <v>53</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="7">
         <v>799</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="3">
         <v>1071</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="3">
         <v>63</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>45782</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" s="3">
         <v>5</v>
       </c>
-      <c r="H66" t="s">
-        <v>60</v>
-      </c>
-      <c r="J66" s="19">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="H66" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J66" s="25">
+        <f t="shared" ref="J66:J75" si="1">COUNTIF(H66,"OBLIGATORIO")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
         <v>54</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="7">
         <v>932</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="3">
         <v>1057</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="3">
         <v>76</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="4">
         <v>45784</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67" s="3">
         <v>5</v>
       </c>
-      <c r="H67" t="s">
-        <v>60</v>
-      </c>
-      <c r="J67" s="19"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="H67" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J67" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
         <v>55</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="3">
+        <v>912</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="3">
+        <v>79</v>
+      </c>
+      <c r="F68" s="4">
+        <v>45785</v>
+      </c>
+      <c r="G68" s="3">
+        <v>6</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J68" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>56</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="1">
-        <v>912</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E68" s="1">
-        <v>79</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45785</v>
-      </c>
-      <c r="G68" s="1">
+      <c r="C69" s="3">
+        <v>911</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="3">
+        <v>62</v>
+      </c>
+      <c r="F69" s="4">
+        <v>45796</v>
+      </c>
+      <c r="G69" s="3">
         <v>6</v>
       </c>
-      <c r="H68" t="s">
-        <v>60</v>
-      </c>
-      <c r="J68" s="19"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>56</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" s="1">
-        <v>911</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E69" s="1">
-        <v>62</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45796</v>
-      </c>
-      <c r="G69" s="1">
-        <v>6</v>
-      </c>
-      <c r="H69" t="s">
-        <v>60</v>
-      </c>
-      <c r="J69" s="19"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H69" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J69" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
-      <c r="B70" s="17"/>
+      <c r="B70" s="5"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="J70" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
         <v>57</v>
       </c>
-      <c r="B71" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" s="1">
+      <c r="B71" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="3">
         <v>2860</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="3">
         <v>74</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="4">
         <v>45835</v>
       </c>
-      <c r="G71" s="1">
-        <v>1</v>
-      </c>
-      <c r="H71" t="s">
-        <v>60</v>
-      </c>
-      <c r="J71" s="20">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G71" s="3">
+        <v>1</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J71" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
-      <c r="B72" s="17"/>
+      <c r="B72" s="5"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J72" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>58</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>80</v>
+      <c r="B73" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C73" s="1">
         <v>2586</v>
@@ -2523,24 +2821,29 @@
       <c r="H73" t="s">
         <v>60</v>
       </c>
-      <c r="J73" s="20">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J73" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
-      <c r="B74" s="17"/>
+      <c r="B74" s="5"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="2"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J74" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>59</v>
       </c>
-      <c r="B75" s="17" t="s">
-        <v>79</v>
+      <c r="B75" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="C75" s="1">
         <v>906</v>
@@ -2560,31 +2863,41 @@
       <c r="H75" t="s">
         <v>60</v>
       </c>
-      <c r="J75" s="20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B76" s="18"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J75" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B76" s="6"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G78" s="1">
         <f>SUM(G1:G75)</f>
         <v>262</v>
       </c>
+      <c r="H78" s="25">
+        <f>COUNTIF(H1:H75,"OBLIGATORIO")</f>
+        <v>50</v>
+      </c>
+      <c r="J78" s="25">
+        <f>COUNTIF(J1:J75,"1")</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H79">
+        <f>COUNTIF(H1:H75,"OPTATIVO")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H80">
+        <f>SUM(H78:H79)</f>
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="J58:J61"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="J66:J69"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="J29:J34"/>
-    <mergeCell ref="J38:J45"/>
-    <mergeCell ref="J49:J53"/>
-    <mergeCell ref="J55:J56"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
